--- a/backend/reports/Candidate_Report.xlsx
+++ b/backend/reports/Candidate_Report.xlsx
@@ -469,43 +469,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aarav Sharma</t>
+          <t>Ethan Matthew D'Souza</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
         <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>aarav.sharma@email.com</t>
+          <t>ethan.dsouza.dev@gmail.com</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+91 98765 43210</t>
+          <t>+91 98765 81425</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - ABC Tech (2023-Present): Built predictive models, developed Django APIs, deployed TensorFlow models, improved accuracy by 15%, automated ETL pipelines.</t>
+          <t>Python Backend Developer - FinEdge Technologies Pvt. Ltd. (Jun 2023-Present)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Python, SQL, Bash, Machine Learning, Deep Learning, TensorFlow, Keras, Scikit-learn, Pandas, NumPy, OpenCV, NLP, Matplotlib, Seaborn, Django, Flask, FastAPI, MySQL, PostgreSQL, SQLite, MongoDB, Git, GitHub, Docker, Linux, Streamlit, Jupyter, VS Code, REST APIs</t>
+          <t>Python, FastAPI, Django, Flask, PostgreSQL, MySQL, MongoDB, Redis, REST APIs, JWT, OAuth2, Docker, Kubernetes, AWS, Git, GitHub Actions</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PyTorch, AWS/Cloud Platforms, CI/CD Pipelines, Unit Testing (PyTest), System Design, Kubernetes</t>
+          <t>Machine Learning, TensorFlow, PyTorch, Pandas, Scikit-learn, Data Preprocessing, Model Evaluation</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>

--- a/backend/reports/Candidate_Report.xlsx
+++ b/backend/reports/Candidate_Report.xlsx
@@ -476,11 +476,11 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D2" t="n">
         <v>82</v>
       </c>
-      <c r="D2" t="n">
-        <v>85</v>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>ethan.dsouza.dev@gmail.com</t>
@@ -493,7 +493,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Python Backend Developer - FinEdge Technologies Pvt. Ltd. (Jun 2023-Present)</t>
+          <t>Python Backend Developer - FinEdge Technologies Pvt. Ltd. (Jun 2023-Present): Developed scalable backend services, optimized APIs by 42%, implemented Redis caching, integrated payment gateways and KYC APIs, improved deployment with CI/CD.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Machine Learning, TensorFlow, PyTorch, Pandas, Scikit-learn, Data Preprocessing, Model Evaluation</t>
+          <t>NumPy, Pandas, Scikit-learn, TensorFlow, PyTorch, Unit Testing</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
